--- a/src/Features/Integration/data/2025_sem2/fr/2.xlsx
+++ b/src/Features/Integration/data/2025_sem2/fr/2.xlsx
@@ -2415,11 +2415,11 @@
       <c r="K34" s="13"/>
       <c r="L34" s="14" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," I: Design soft. (lab), 
-G-C. Stănescu, 326/6
+G-C. Stănescu, 326/4
  II: Cloud comp. (lab), 
 A. Prepeliță, 251/4")</f>
         <v xml:space="preserve"> I: Design soft. (lab), 
-G-C. Stănescu, 326/6
+G-C. Stănescu, 326/4
  II: Cloud comp. (lab), 
 A. Prepeliță, 251/4</v>
       </c>
